--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Lab Observation: Microbiology Bacteriology Observationsputum</t>
+    <t>Lab Observation: Microbiology Bacteriology Observation[sputum]</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-observation-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-observation-lab.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$56</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2303" uniqueCount="481">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -594,6 +594,9 @@
     <t>http://hl7.org/fhir/ValueSet/observation-status</t>
   </si>
   <si>
+    <t>2082: target not supported</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -639,6 +642,9 @@
   </si>
   <si>
     <t>open</t>
+  </si>
+  <si>
+    <t>2083: target not supported</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -661,6 +667,9 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>2084: target not supported</t>
+  </si>
+  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -689,6 +698,9 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
+    <t>2085: target not supported</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -726,6 +738,9 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
+    <t>2086: target not supported</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -815,6 +830,10 @@
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">us-core-1
 </t>
   </si>
@@ -835,6 +854,19 @@
     <t>FiveWs.done[x]</t>
   </si>
   <si>
+    <t>Observation.effective[x]:effectiveDateTime</t>
+  </si>
+  <si>
+    <t>effectiveDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>2087: target not supported</t>
+  </si>
+  <si>
     <t>Observation.issued</t>
   </si>
   <si>
@@ -907,10 +939,6 @@
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
     <t>obs-7
 us-core-2us-core-3us-core-4</t>
   </si>
@@ -947,6 +975,28 @@
     <t>Micro.Microbiology.SputumScreen</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>2088: target not supported</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>2089: target not supported</t>
+  </si>
+  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -968,6 +1018,9 @@
   <si>
     <t>obs-6
 us-core-2</t>
+  </si>
+  <si>
+    <t>2090: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -1793,12 +1846,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR53"/>
+  <dimension ref="A1:AR56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -3589,25 +3642,25 @@
         <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>84</v>
+        <v>185</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AR14" t="s" s="2">
         <v>84</v>
@@ -3615,10 +3668,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3641,19 +3694,19 @@
         <v>84</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>84</v>
@@ -3681,26 +3734,26 @@
         <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -3715,7 +3768,7 @@
         <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>84</v>
@@ -3730,10 +3783,10 @@
         <v>84</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -3741,13 +3794,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>84</v>
@@ -3769,19 +3822,19 @@
         <v>84</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>84</v>
@@ -3791,7 +3844,7 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>84</v>
@@ -3809,10 +3862,10 @@
         <v>118</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>84</v>
@@ -3830,7 +3883,7 @@
         <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -3845,7 +3898,7 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>84</v>
+        <v>207</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>84</v>
@@ -3860,10 +3913,10 @@
         <v>84</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -3871,14 +3924,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3897,19 +3950,19 @@
         <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>84</v>
@@ -3934,13 +3987,13 @@
         <v>84</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>84</v>
@@ -3958,7 +4011,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>94</v>
@@ -3973,36 +4026,36 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>84</v>
+        <v>217</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4025,19 +4078,19 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>84</v>
@@ -4086,7 +4139,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4101,25 +4154,25 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>84</v>
@@ -4127,10 +4180,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4153,16 +4206,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4212,7 +4265,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4239,13 +4292,13 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>84</v>
@@ -4253,14 +4306,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4279,19 +4332,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4340,7 +4393,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4361,19 +4414,19 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>84</v>
@@ -4381,14 +4434,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4407,19 +4460,19 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -4456,19 +4509,17 @@
         <v>84</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4477,10 +4528,10 @@
         <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>84</v>
@@ -4489,19 +4540,19 @@
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4509,14 +4560,16 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="D22" t="s" s="2">
-        <v>84</v>
+        <v>253</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4526,7 +4579,7 @@
         <v>94</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>84</v>
@@ -4535,18 +4588,20 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>84</v>
       </c>
@@ -4594,7 +4649,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4603,31 +4658,31 @@
         <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>84</v>
+        <v>260</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>106</v>
+        <v>261</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>84</v>
+        <v>269</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO22" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AP22" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4635,10 +4690,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4649,7 +4704,7 @@
         <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>84</v>
@@ -4661,18 +4716,18 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>84</v>
       </c>
@@ -4720,13 +4775,13 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>84</v>
@@ -4741,19 +4796,19 @@
         <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>273</v>
+        <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4761,10 +4816,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4775,10 +4830,10 @@
         <v>82</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>84</v>
@@ -4787,17 +4842,15 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N24" t="s" s="2">
         <v>281</v>
       </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
         <v>282</v>
       </c>
@@ -4836,65 +4889,65 @@
         <v>84</v>
       </c>
       <c r="AB24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AC24" s="2"/>
-      <c r="AD24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AJ24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AK24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AO24" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AR24" t="s" s="2">
-        <v>289</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>84</v>
       </c>
@@ -4915,19 +4968,19 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="O25" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -4964,19 +5017,17 @@
         <v>84</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -4985,44 +5036,46 @@
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>293</v>
+        <v>84</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>294</v>
+        <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>84</v>
       </c>
@@ -5040,22 +5093,22 @@
         <v>84</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>191</v>
+        <v>301</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5080,11 +5133,13 @@
         <v>84</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>300</v>
+        <v>84</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>84</v>
@@ -5102,7 +5157,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5111,77 +5166,79 @@
         <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>106</v>
+        <v>294</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>84</v>
+        <v>302</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>84</v>
+        <v>295</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>137</v>
+        <v>296</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>84</v>
+        <v>298</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="D27" t="s" s="2">
-        <v>304</v>
+        <v>84</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>191</v>
+        <v>306</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5206,13 +5263,13 @@
         <v>84</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>211</v>
+        <v>84</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>309</v>
+        <v>84</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>310</v>
+        <v>84</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>84</v>
@@ -5230,22 +5287,22 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>106</v>
+        <v>294</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>84</v>
+        <v>307</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>84</v>
@@ -5254,29 +5311,31 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>314</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>84</v>
       </c>
@@ -5285,31 +5344,31 @@
         <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>316</v>
+        <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>317</v>
+        <v>289</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>318</v>
+        <v>290</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>319</v>
+        <v>291</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>320</v>
+        <v>292</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5358,22 +5417,22 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>106</v>
+        <v>294</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>84</v>
+        <v>310</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -5382,27 +5441,27 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>84</v>
+        <v>295</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>84</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5416,7 +5475,7 @@
         <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>84</v>
@@ -5425,18 +5484,20 @@
         <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
       </c>
@@ -5460,13 +5521,11 @@
         <v>84</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>84</v>
@@ -5484,7 +5543,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5493,13 +5552,13 @@
         <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>84</v>
+        <v>317</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>84</v>
+        <v>318</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>84</v>
@@ -5508,38 +5567,38 @@
         <v>84</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>330</v>
+        <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>331</v>
+        <v>137</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>333</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>321</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>84</v>
@@ -5551,19 +5610,19 @@
         <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5588,14 +5647,14 @@
         <v>84</v>
       </c>
       <c r="X30" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Z30" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="Y30" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>340</v>
-      </c>
       <c r="AA30" t="s" s="2">
         <v>84</v>
       </c>
@@ -5612,13 +5671,13 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>84</v>
@@ -5636,27 +5695,27 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>84</v>
+        <v>328</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>84</v>
+        <v>331</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5667,7 +5726,7 @@
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>84</v>
@@ -5679,18 +5738,20 @@
         <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
       </c>
@@ -5738,13 +5799,13 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>84</v>
@@ -5762,27 +5823,27 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>348</v>
+        <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>351</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5805,16 +5866,16 @@
         <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>353</v>
+        <v>192</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5840,13 +5901,13 @@
         <v>84</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>84</v>
+        <v>344</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>84</v>
+        <v>345</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>84</v>
+        <v>346</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>84</v>
@@ -5864,7 +5925,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5888,27 +5949,27 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5919,7 +5980,7 @@
         <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>84</v>
@@ -5931,19 +5992,19 @@
         <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>362</v>
+        <v>192</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -5968,13 +6029,13 @@
         <v>84</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>84</v>
+        <v>344</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>84</v>
+        <v>356</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>84</v>
@@ -5992,19 +6053,19 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>367</v>
+        <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>84</v>
@@ -6019,10 +6080,10 @@
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6033,10 +6094,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6059,15 +6120,17 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>292</v>
+        <v>361</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6116,7 +6179,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6128,7 +6191,7 @@
         <v>84</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>84</v>
@@ -6140,38 +6203,38 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>84</v>
+        <v>365</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>84</v>
+        <v>366</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>84</v>
+        <v>368</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>84</v>
@@ -6183,16 +6246,16 @@
         <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>140</v>
+        <v>370</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>141</v>
+        <v>371</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>143</v>
+        <v>373</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6242,43 +6305,43 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AP35" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AQ35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR35" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AQ35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR35" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -6290,7 +6353,7 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>379</v>
+        <v>84</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6303,13 +6366,13 @@
         <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>140</v>
+        <v>379</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>380</v>
@@ -6318,10 +6381,10 @@
         <v>381</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>143</v>
+        <v>382</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>149</v>
+        <v>383</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6370,7 +6433,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6382,7 +6445,7 @@
         <v>84</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>145</v>
+        <v>384</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>84</v>
@@ -6397,10 +6460,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>84</v>
+        <v>385</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>137</v>
+        <v>386</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6411,10 +6474,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6437,13 +6500,13 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>384</v>
+        <v>301</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6494,7 +6557,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6503,10 +6566,10 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>387</v>
+        <v>84</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
@@ -6521,10 +6584,10 @@
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>388</v>
+        <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6535,21 +6598,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>84</v>
@@ -6561,15 +6624,17 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>384</v>
+        <v>140</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>391</v>
+        <v>141</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6618,19 +6683,19 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>387</v>
+        <v>84</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>84</v>
@@ -6645,10 +6710,10 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>388</v>
+        <v>84</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -6659,45 +6724,45 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>84</v>
+        <v>396</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>397</v>
+        <v>143</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>398</v>
+        <v>149</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6722,43 +6787,43 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>394</v>
-      </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>84</v>
@@ -6770,13 +6835,13 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>402</v>
+        <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>313</v>
+        <v>137</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6787,10 +6852,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6801,7 +6866,7 @@
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>84</v>
@@ -6813,20 +6878,16 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>191</v>
+        <v>401</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>84</v>
       </c>
@@ -6850,13 +6911,13 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>327</v>
+        <v>84</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>408</v>
+        <v>84</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>409</v>
+        <v>84</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -6874,16 +6935,16 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>84</v>
+        <v>404</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>106</v>
@@ -6898,13 +6959,13 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>313</v>
+        <v>406</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -6915,10 +6976,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6941,18 +7002,16 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>414</v>
-      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>84</v>
       </c>
@@ -7000,7 +7059,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7009,7 +7068,7 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>84</v>
+        <v>404</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>106</v>
@@ -7027,10 +7086,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>84</v>
+        <v>405</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7041,10 +7100,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7067,16 +7126,20 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>292</v>
+        <v>192</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7100,13 +7163,13 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>84</v>
+        <v>416</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>84</v>
+        <v>417</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -7124,7 +7187,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7148,13 +7211,13 @@
         <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>84</v>
+        <v>418</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>388</v>
+        <v>419</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>419</v>
+        <v>330</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7188,21 +7251,23 @@
         <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>84</v>
       </c>
@@ -7226,13 +7291,13 @@
         <v>84</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>84</v>
+        <v>344</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>84</v>
+        <v>425</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>84</v>
+        <v>426</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>84</v>
@@ -7274,13 +7339,13 @@
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>84</v>
+        <v>418</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>426</v>
+        <v>330</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7305,7 +7370,7 @@
         <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>84</v>
@@ -7314,7 +7379,7 @@
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>428</v>
@@ -7325,10 +7390,10 @@
       <c r="M44" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
@@ -7382,7 +7447,7 @@
         <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>84</v>
@@ -7403,7 +7468,7 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>425</v>
+        <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>432</v>
@@ -7431,7 +7496,7 @@
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>84</v>
@@ -7440,10 +7505,10 @@
         <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>362</v>
+        <v>301</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>434</v>
@@ -7451,12 +7516,8 @@
       <c r="M45" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="N45" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>437</v>
-      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>84</v>
       </c>
@@ -7510,7 +7571,7 @@
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>84</v>
@@ -7531,10 +7592,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>438</v>
+        <v>405</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7545,10 +7606,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7559,7 +7620,7 @@
         <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>84</v>
@@ -7568,18 +7629,20 @@
         <v>84</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>292</v>
+        <v>438</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>371</v>
+        <v>439</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -7628,19 +7691,19 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>373</v>
+        <v>437</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>84</v>
@@ -7655,10 +7718,10 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>84</v>
+        <v>442</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>374</v>
+        <v>443</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7669,14 +7732,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7692,19 +7755,19 @@
         <v>84</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>140</v>
+        <v>445</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>141</v>
+        <v>446</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>376</v>
+        <v>447</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>143</v>
+        <v>448</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7754,7 +7817,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>377</v>
+        <v>444</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7766,7 +7829,7 @@
         <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>84</v>
@@ -7781,10 +7844,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>84</v>
+        <v>442</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>374</v>
+        <v>449</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -7795,14 +7858,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>379</v>
+        <v>84</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7815,25 +7878,25 @@
         <v>84</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>140</v>
+        <v>379</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>380</v>
+        <v>451</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>381</v>
+        <v>452</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>143</v>
+        <v>453</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>149</v>
+        <v>454</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -7882,7 +7945,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>382</v>
+        <v>450</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7894,7 +7957,7 @@
         <v>84</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>84</v>
@@ -7909,10 +7972,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>84</v>
+        <v>455</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>137</v>
+        <v>456</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -7923,10 +7986,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7934,7 +7997,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>94</v>
@@ -7946,23 +8009,19 @@
         <v>84</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>191</v>
+        <v>301</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>444</v>
+        <v>388</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
@@ -7986,13 +8045,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>327</v>
+        <v>84</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>447</v>
+        <v>84</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>213</v>
+        <v>84</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8010,10 +8069,10 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>443</v>
+        <v>390</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>94</v>
@@ -8022,7 +8081,7 @@
         <v>84</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>84</v>
@@ -8034,16 +8093,16 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>448</v>
+        <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>216</v>
+        <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>217</v>
+        <v>391</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>218</v>
+        <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>84</v>
@@ -8051,21 +8110,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>84</v>
@@ -8074,23 +8133,21 @@
         <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>278</v>
+        <v>140</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>450</v>
+        <v>141</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>451</v>
+        <v>393</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8138,19 +8195,19 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>449</v>
+        <v>394</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>84</v>
@@ -8162,62 +8219,62 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>453</v>
+        <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>287</v>
+        <v>84</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>288</v>
+        <v>391</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>289</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>84</v>
+        <v>396</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>455</v>
+        <v>397</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>456</v>
+        <v>398</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>457</v>
+        <v>143</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>299</v>
+        <v>149</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8242,13 +8299,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>211</v>
+        <v>84</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>458</v>
+        <v>84</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>300</v>
+        <v>84</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8266,19 +8323,19 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>454</v>
+        <v>399</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>459</v>
+        <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -8293,10 +8350,10 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8314,14 +8371,14 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>304</v>
+        <v>84</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>84</v>
@@ -8330,22 +8387,22 @@
         <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>305</v>
+        <v>461</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>306</v>
+        <v>462</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>307</v>
+        <v>463</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>308</v>
+        <v>213</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8370,13 +8427,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>211</v>
+        <v>344</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>309</v>
+        <v>464</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>310</v>
+        <v>216</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -8397,10 +8454,10 @@
         <v>460</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>84</v>
@@ -8418,27 +8475,27 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>311</v>
+        <v>465</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>312</v>
+        <v>220</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>313</v>
+        <v>221</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>84</v>
+        <v>222</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>314</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8449,7 +8506,7 @@
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>84</v>
@@ -8458,22 +8515,22 @@
         <v>84</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>85</v>
+        <v>288</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>365</v>
+        <v>469</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>366</v>
+        <v>292</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -8522,13 +8579,13 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>84</v>
@@ -8546,23 +8603,407 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>84</v>
+        <v>470</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>368</v>
+        <v>296</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>369</v>
+        <v>297</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR54" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR55" t="s" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR56" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR53">
+  <autoFilter ref="A1:AR56">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8572,7 +9013,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI52">
+  <conditionalFormatting sqref="A2:AI55">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -969,7 +969,7 @@
 </t>
   </si>
   <si>
-    <t>1517: source value from MICROBIOLOGY - SPUTUM SCREEN (63.05-11.58)</t>
+    <t>1517: source value based on MICROBIOLOGY - SPUTUM SCREEN (63.05-11.58)</t>
   </si>
   <si>
     <t>Micro.Microbiology.SputumScreen</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$54</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2303" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2219" uniqueCount="473">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -642,9 +642,6 @@
   </si>
   <si>
     <t>open</t>
-  </si>
-  <si>
-    <t>2083: target not supported</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -973,28 +970,6 @@
   </si>
   <si>
     <t>Micro.Microbiology.SputumScreen</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>2088: target not supported</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>2089: target not supported</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1846,12 +1821,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR56"/>
+  <dimension ref="A1:AR54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -3768,25 +3743,25 @@
         <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AL15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP15" t="s" s="2">
+      <c r="AQ15" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -3794,13 +3769,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>84</v>
@@ -3844,7 +3819,7 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>84</v>
@@ -3898,7 +3873,7 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>84</v>
@@ -3913,10 +3888,10 @@
         <v>84</v>
       </c>
       <c r="AP16" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AQ16" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AQ16" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -3924,14 +3899,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3953,16 +3928,16 @@
         <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>84</v>
@@ -3987,14 +3962,14 @@
         <v>84</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>216</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>84</v>
       </c>
@@ -4011,7 +3986,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>94</v>
@@ -4026,36 +4001,36 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AP17" t="s" s="2">
+      <c r="AQ17" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AQ17" t="s" s="2">
+      <c r="AR17" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AR17" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4078,19 +4053,19 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>84</v>
@@ -4139,7 +4114,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4154,25 +4129,25 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AN18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AP18" t="s" s="2">
+      <c r="AQ18" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AQ18" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>84</v>
@@ -4180,10 +4155,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4206,16 +4181,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4265,7 +4240,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4292,13 +4267,13 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>84</v>
@@ -4306,14 +4281,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4332,19 +4307,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4393,7 +4368,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4414,19 +4389,19 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AN20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AP20" t="s" s="2">
+      <c r="AQ20" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>84</v>
@@ -4434,14 +4409,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4460,19 +4435,19 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -4509,7 +4484,7 @@
         <v>84</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
@@ -4519,7 +4494,7 @@
         <v>200</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4528,31 +4503,31 @@
         <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AJ21" t="s" s="2">
+      <c r="AK21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AK21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AN21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AP21" t="s" s="2">
+      <c r="AQ21" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4560,16 +4535,16 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C22" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="B22" t="s" s="2">
+      <c r="D22" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="D22" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4588,19 +4563,19 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>84</v>
@@ -4649,7 +4624,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4658,31 +4633,31 @@
         <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AJ22" t="s" s="2">
+      <c r="AK22" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AK22" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AN22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AP22" t="s" s="2">
+      <c r="AQ22" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4690,10 +4665,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4716,16 +4691,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4775,7 +4750,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4802,13 +4777,13 @@
         <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AP23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4816,10 +4791,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4842,17 +4817,17 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -4901,7 +4876,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -4922,19 +4897,19 @@
         <v>84</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AN24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AP24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -4942,10 +4917,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4968,19 +4943,19 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5017,7 +4992,7 @@
         <v>84</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
@@ -5027,7 +5002,7 @@
         <v>200</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5036,45 +5011,45 @@
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AJ25" t="s" s="2">
+      <c r="AK25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AK25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AP25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR25" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>298</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="C26" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>84</v>
@@ -5096,19 +5071,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5157,7 +5132,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5166,46 +5141,44 @@
         <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AJ26" t="s" s="2">
+      <c r="AK26" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AK26" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AP26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR26" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>298</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>84</v>
       </c>
@@ -5223,22 +5196,22 @@
         <v>84</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>291</v>
-      </c>
       <c r="O27" t="s" s="2">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5263,13 +5236,11 @@
         <v>84</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>84</v>
+        <v>308</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>84</v>
@@ -5287,7 +5258,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5296,13 +5267,13 @@
         <v>94</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>294</v>
+        <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>84</v>
@@ -5311,64 +5282,62 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>295</v>
+        <v>84</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>296</v>
+        <v>137</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>298</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>84</v>
+        <v>313</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5393,13 +5362,13 @@
         <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>84</v>
+        <v>213</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>84</v>
+        <v>318</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>84</v>
+        <v>319</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
@@ -5417,22 +5386,22 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>293</v>
+        <v>84</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>294</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>310</v>
+        <v>84</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -5441,27 +5410,27 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>298</v>
+        <v>323</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5472,10 +5441,10 @@
         <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>84</v>
@@ -5484,19 +5453,19 @@
         <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>192</v>
+        <v>325</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5521,11 +5490,13 @@
         <v>84</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>316</v>
+        <v>84</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>84</v>
@@ -5543,22 +5514,22 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>317</v>
+        <v>84</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>318</v>
+        <v>84</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>84</v>
@@ -5570,10 +5541,10 @@
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>137</v>
+        <v>330</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5584,21 +5555,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>321</v>
+        <v>84</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>84</v>
@@ -5613,17 +5584,15 @@
         <v>192</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>84</v>
       </c>
@@ -5647,13 +5616,13 @@
         <v>84</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>214</v>
+        <v>336</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>84</v>
@@ -5671,13 +5640,13 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>84</v>
@@ -5695,27 +5664,27 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>331</v>
+        <v>342</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5726,7 +5695,7 @@
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>84</v>
@@ -5738,19 +5707,19 @@
         <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>333</v>
+        <v>192</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -5775,13 +5744,13 @@
         <v>84</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>84</v>
+        <v>336</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>84</v>
+        <v>348</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>84</v>
+        <v>349</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>84</v>
@@ -5799,13 +5768,13 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>84</v>
@@ -5826,10 +5795,10 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -5840,10 +5809,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5866,16 +5835,16 @@
         <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>192</v>
+        <v>353</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5901,13 +5870,13 @@
         <v>84</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>344</v>
+        <v>84</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>345</v>
+        <v>84</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>346</v>
+        <v>84</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>84</v>
@@ -5925,7 +5894,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5949,27 +5918,27 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>350</v>
+        <v>360</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5992,20 +5961,18 @@
         <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>192</v>
+        <v>362</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>84</v>
       </c>
@@ -6029,13 +5996,13 @@
         <v>84</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>344</v>
+        <v>84</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>356</v>
+        <v>84</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>357</v>
+        <v>84</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>84</v>
@@ -6053,7 +6020,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6077,27 +6044,27 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>84</v>
+        <v>366</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>84</v>
+        <v>369</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6108,7 +6075,7 @@
         <v>82</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>84</v>
@@ -6120,18 +6087,20 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
       </c>
@@ -6179,19 +6148,19 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>106</v>
+        <v>376</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>84</v>
@@ -6203,27 +6172,27 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>365</v>
+        <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>368</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6246,17 +6215,15 @@
         <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6305,7 +6272,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6317,7 +6284,7 @@
         <v>84</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>84</v>
@@ -6329,31 +6296,31 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>375</v>
+        <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>377</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6372,20 +6339,18 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>379</v>
+        <v>140</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>380</v>
+        <v>141</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>84</v>
       </c>
@@ -6433,7 +6398,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6445,7 +6410,7 @@
         <v>84</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>384</v>
+        <v>145</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>84</v>
@@ -6460,10 +6425,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>385</v>
+        <v>84</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6481,35 +6446,39 @@
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>84</v>
+        <v>388</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>301</v>
+        <v>140</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
       </c>
@@ -6557,19 +6526,19 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
@@ -6587,7 +6556,7 @@
         <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>391</v>
+        <v>137</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6605,14 +6574,14 @@
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>84</v>
@@ -6624,17 +6593,15 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>140</v>
+        <v>393</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>141</v>
+        <v>394</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6683,19 +6650,19 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>84</v>
+        <v>396</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>84</v>
@@ -6710,10 +6677,10 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>84</v>
+        <v>397</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -6724,46 +6691,42 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>396</v>
+        <v>84</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>140</v>
+        <v>393</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>84</v>
       </c>
@@ -6817,13 +6780,13 @@
         <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>84</v>
+        <v>396</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>84</v>
@@ -6838,10 +6801,10 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>84</v>
+        <v>397</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>137</v>
+        <v>402</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6852,10 +6815,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6878,16 +6841,20 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>401</v>
+        <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
       </c>
@@ -6911,13 +6878,13 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>84</v>
+        <v>408</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>84</v>
+        <v>409</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -6935,7 +6902,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -6944,7 +6911,7 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>106</v>
@@ -6959,13 +6926,13 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>84</v>
+        <v>410</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>406</v>
+        <v>322</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -6976,10 +6943,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6990,7 +6957,7 @@
         <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>84</v>
@@ -7002,16 +6969,20 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>401</v>
+        <v>192</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
       </c>
@@ -7035,13 +7006,13 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>84</v>
+        <v>336</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>84</v>
+        <v>417</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>84</v>
+        <v>418</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -7059,16 +7030,16 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>106</v>
@@ -7083,13 +7054,13 @@
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>84</v>
+        <v>410</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>410</v>
+        <v>322</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7100,10 +7071,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7126,19 +7097,17 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>192</v>
+        <v>420</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>414</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
@@ -7163,13 +7132,13 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>416</v>
+        <v>84</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>417</v>
+        <v>84</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -7187,7 +7156,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7211,13 +7180,13 @@
         <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>419</v>
+        <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>330</v>
+        <v>424</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7228,10 +7197,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7242,7 +7211,7 @@
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>84</v>
@@ -7254,20 +7223,16 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>192</v>
+        <v>300</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>84</v>
       </c>
@@ -7291,37 +7256,37 @@
         <v>84</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>344</v>
+        <v>84</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>420</v>
-      </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>84</v>
@@ -7339,13 +7304,13 @@
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>330</v>
+        <v>428</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7356,10 +7321,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7370,7 +7335,7 @@
         <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>84</v>
@@ -7379,21 +7344,21 @@
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
@@ -7441,13 +7406,13 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>84</v>
@@ -7468,10 +7433,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>84</v>
+        <v>434</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7482,10 +7447,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7496,7 +7461,7 @@
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>84</v>
@@ -7505,18 +7470,20 @@
         <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>301</v>
+        <v>437</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7565,13 +7532,13 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>84</v>
@@ -7592,10 +7559,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>405</v>
+        <v>434</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7606,10 +7573,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7632,18 +7599,20 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>438</v>
+        <v>371</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
@@ -7691,7 +7660,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7718,10 +7687,10 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7732,10 +7701,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7746,7 +7715,7 @@
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>84</v>
@@ -7755,20 +7724,18 @@
         <v>84</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>445</v>
+        <v>300</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>446</v>
+        <v>380</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -7817,19 +7784,19 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>444</v>
+        <v>382</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>84</v>
@@ -7844,10 +7811,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>442</v>
+        <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>449</v>
+        <v>383</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -7865,7 +7832,7 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7881,23 +7848,21 @@
         <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>379</v>
+        <v>140</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>451</v>
+        <v>141</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>452</v>
+        <v>385</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -7945,7 +7910,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>450</v>
+        <v>386</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7957,7 +7922,7 @@
         <v>84</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>84</v>
@@ -7972,10 +7937,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>455</v>
+        <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>456</v>
+        <v>383</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -7986,42 +7951,46 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>84</v>
+        <v>388</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>301</v>
+        <v>140</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8069,19 +8038,19 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>84</v>
@@ -8099,7 +8068,7 @@
         <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>391</v>
+        <v>137</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8110,21 +8079,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>84</v>
@@ -8133,21 +8102,23 @@
         <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>141</v>
+        <v>453</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>393</v>
+        <v>454</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8171,13 +8142,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>84</v>
+        <v>336</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>84</v>
+        <v>456</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8195,19 +8166,19 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>394</v>
+        <v>452</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>84</v>
@@ -8219,16 +8190,16 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>84</v>
+        <v>457</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>84</v>
+        <v>219</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>391</v>
+        <v>220</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>84</v>
+        <v>221</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>84</v>
@@ -8236,45 +8207,45 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>396</v>
+        <v>84</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>140</v>
+        <v>287</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>397</v>
+        <v>459</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>398</v>
+        <v>460</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>143</v>
+        <v>461</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>149</v>
+        <v>291</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8323,19 +8294,19 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>399</v>
+        <v>458</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -8347,27 +8318,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>84</v>
+        <v>295</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>137</v>
+        <v>296</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>84</v>
+        <v>297</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8375,7 +8346,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>94</v>
@@ -8387,22 +8358,22 @@
         <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>213</v>
+        <v>307</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8427,13 +8398,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>344</v>
+        <v>213</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>216</v>
+        <v>308</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -8451,16 +8422,16 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>84</v>
+        <v>468</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8475,16 +8446,16 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>465</v>
+        <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>221</v>
+        <v>311</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>222</v>
+        <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>84</v>
@@ -8492,21 +8463,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>84</v>
+        <v>313</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>84</v>
@@ -8515,22 +8486,22 @@
         <v>84</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>288</v>
+        <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>467</v>
+        <v>314</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>468</v>
+        <v>315</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>469</v>
+        <v>316</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -8555,13 +8526,13 @@
         <v>84</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>84</v>
+        <v>213</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>84</v>
+        <v>318</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>84</v>
+        <v>319</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
@@ -8579,13 +8550,13 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>84</v>
@@ -8603,27 +8574,27 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>470</v>
+        <v>320</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>298</v>
+        <v>323</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8634,7 +8605,7 @@
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>84</v>
@@ -8646,19 +8617,19 @@
         <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>473</v>
-      </c>
       <c r="N54" t="s" s="2">
-        <v>474</v>
+        <v>374</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>315</v>
+        <v>375</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -8683,13 +8654,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>475</v>
+        <v>84</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>316</v>
+        <v>84</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -8707,16 +8678,16 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>476</v>
+        <v>84</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -8734,276 +8705,20 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>137</v>
+        <v>377</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>319</v>
+        <v>378</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="P55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR55" t="s" s="2">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="P56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AQ56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR56" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR56">
+  <autoFilter ref="A1:AR54">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9013,7 +8728,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI55">
+  <conditionalFormatting sqref="A2:AI53">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationsputum.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
